--- a/Result/checksun_type/導線架.xlsx
+++ b/Result/checksun_type/導線架.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,22 +1668,22 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>50.065</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>49.02</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>49.87</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>49.02</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2675,12 +2679,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>49.92</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>48.99</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>49.87</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>48.99</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,22 +3655,22 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>49.845</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>48.93</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>49.87</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>48.93</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,22 +4641,22 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>49.845</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>49.87</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>48.86</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>49.87</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>48.86</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,22 +5627,22 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>49.775</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>48.83</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>49.96</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>48.83</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,22 +6613,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>49.75</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>50.01</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>48.86</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>50.01</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>48.86</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>49.78</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>48.92</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>50.1</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>48.92</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>49.79</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>48.92</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>50.06</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>48.92</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,22 +9571,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>49.79000000000001</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>50.02</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>48.98</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>50.02</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>48.98</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10481,22 +10517,22 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -10506,7 +10542,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -10516,27 +10552,27 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>72.97999999999999</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>72.43000000000001</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>71.56</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>72.43</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>71.56</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -11478,7 +11518,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -11488,7 +11528,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -11498,27 +11538,27 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>72.47</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>72.29000000000001</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>71.45999999999999</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>72.29</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>71.46</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -12455,12 +12499,12 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -12470,37 +12514,37 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>72.49000000000001</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>72.34999999999999</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>71.41</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>72.35</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>71.41</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -13437,12 +13485,12 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -13452,12 +13500,12 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -13467,22 +13515,22 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>72.5</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>71.3</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>72.32</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>71.3</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -14414,17 +14466,17 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -14434,7 +14486,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -14444,27 +14496,27 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>72.32000000000001</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>71.34</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>71.34</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -15396,17 +15452,17 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -15416,7 +15472,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -15426,27 +15482,27 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>72.27</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>72.59</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>71.45999999999999</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>72.59</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>71.46</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -16373,62 +16433,62 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>72.24</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>72.69</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>71.63</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>72.69</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>71.63</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -17360,17 +17424,17 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -17380,37 +17444,37 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>71.94</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>71.77</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>72.52</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>71.77</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18342,17 +18410,17 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>71.97</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>72</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>72.4</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19319,62 +19391,62 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>92.30999999999999</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>82.08</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>88.78</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>82.08</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -19689,7 +19765,7 @@
       </c>
       <c r="DQ20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR20" t="inlineStr">
@@ -20311,12 +20387,12 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -20326,37 +20402,37 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>90.81</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>81.75</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>81.75</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -20671,7 +20751,7 @@
       </c>
       <c r="DQ21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR21" t="inlineStr">
@@ -21288,57 +21368,57 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>89.73</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>87.67</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>81.47</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>87.67</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>81.47</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22270,57 +22354,57 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>89.47</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>87.22</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>81.27</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>87.22</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>81.27</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23247,62 +23335,62 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>88.67</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>86.86</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>81.16</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>86.86</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>81.16</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24229,62 +24321,62 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>88.06</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>86.56999999999999</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>81.20999999999999</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>86.57</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>81.21</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25211,62 +25307,62 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AW26" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>87.24</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>86.08</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>81.23999999999999</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>86.08</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>81.24</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26193,62 +26293,62 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>86.47999999999999</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>85.31999999999999</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>81.15000000000001</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>85.32</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>81.15</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27175,62 +27279,62 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>86.08</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>84.63</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>81.23999999999999</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>84.63</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>81.24</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28172,47 +28280,47 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>224.85</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>231.18</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>200.66</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>231.18</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>200.66</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29154,7 +29266,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,22 +29291,22 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>227.3</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>232.05</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>199.79</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>232.05</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>199.79</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30136,7 +30252,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,22 +30277,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>231.2</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>232.72</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>198.81</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>232.72</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>198.81</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31118,7 +31238,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31263,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>236.0</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>233.9</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>197.75</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>233.9</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>197.75</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32095,12 +32219,12 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32120,27 +32244,27 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>237.85</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>235.1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>196.89</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>235.1</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>196.89</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33077,52 +33205,52 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>239.45</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>236.12</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>196.33</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>236.12</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>196.33</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34054,17 +34186,17 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
@@ -34074,37 +34206,37 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>240.6</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>235.78</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>195.82</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>235.78</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>195.82</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35036,57 +35172,57 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr">
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>239.5</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>233.82</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>194.94</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>233.82</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>194.94</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36013,62 +36153,62 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>239.2</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>232.02</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>194.42</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>232.02</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>194.42</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
